--- a/docs/03_test/部署一覧画面テスト.xlsx
+++ b/docs/03_test/部署一覧画面テスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A7F2A0-529C-45FC-836A-E332903EFAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCBB0DB-47EA-4E8E-8EE1-5905E6FA1B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
@@ -340,7 +340,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -377,12 +377,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -406,6 +400,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -921,21 +924,21 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="11"/>
@@ -948,20 +951,20 @@
         <v>15</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="13"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="8" t="s">
@@ -1016,7 +1019,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="7"/>
-      <c r="C25" s="18"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
@@ -1024,67 +1027,67 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="20"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="21"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="20"/>
+      <c r="A37" s="19"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="16"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="20"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="18"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="16"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="20"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="20"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="16"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="20"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="18"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="16"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="20"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="18"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="16"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="20"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="16"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="20"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="4"/>
@@ -1095,7 +1098,7 @@
       <c r="C47" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="A18:B18"/>
@@ -1107,8 +1110,6 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/03_test/部署一覧画面テスト.xlsx
+++ b/docs/03_test/部署一覧画面テスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCBB0DB-47EA-4E8E-8EE1-5905E6FA1B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B6EA05-D112-4B38-93A0-E92B24732438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
@@ -63,22 +63,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部署番号フォームの下:「部署番号は入力必須です」</t>
-    <rPh sb="0" eb="4">
-      <t>ブショバンゴウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>ブショバンゴウ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>ニュウリョクヒッス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テストの対象と範囲</t>
     <rPh sb="4" eb="6">
       <t>タイショウ</t>
@@ -107,10 +91,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部署番号フォームの下:「部署番号は100～999までの数字で入力して下さい」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>結果画面のスクリーンショット</t>
     <rPh sb="0" eb="2">
       <t>ケッカ</t>
@@ -207,6 +187,38 @@
       <t>コ</t>
     </rPh>
     <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上記のデータが表示されている</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「部署が登録されていないません」と「部署を登録する」の二つのメッセージ、リンクが表示</t>
+    <rPh sb="1" eb="3">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -340,7 +352,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -362,6 +374,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -371,44 +395,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -898,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1251DAA0-F3BC-4BF2-9758-9F61521A72EB}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="3" width="49.08203125" customWidth="1"/>
@@ -907,97 +904,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="7"/>
+      <c r="A1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="11"/>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8"/>
+      <c r="A3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
+        <v>6</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="15"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="13"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1">
         <v>1</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1005,111 +994,90 @@
         <v>2</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="16"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="19"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="18"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="14"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="14"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="18"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="18"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="14"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="18"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="14"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="18"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="14"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="18"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="14"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="18"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="8"/>
+      <c r="B37" s="4"/>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7"/>
+      <c r="B38" s="4"/>
+      <c r="D38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7"/>
+      <c r="B39" s="4"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="D40" s="7"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7"/>
+      <c r="B41" s="4"/>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7"/>
+      <c r="B42" s="4"/>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7"/>
+      <c r="B43" s="4"/>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7"/>
+      <c r="B44" s="4"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="4"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/03_test/部署一覧画面テスト.xlsx
+++ b/docs/03_test/部署一覧画面テスト.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B6EA05-D112-4B38-93A0-E92B24732438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C3BE9A-1BCD-4C9D-A424-A3664613A816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EDAA8412-2266-41CD-B1C8-4C46E6C24210}"/>
   </bookViews>
   <sheets>
-    <sheet name="部署登録テスト" sheetId="1" r:id="rId1"/>
+    <sheet name="部署一覧テスト" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -395,6 +395,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -402,9 +405,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -936,10 +936,10 @@
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11" t="s">
@@ -950,16 +950,16 @@
       <c r="D7" s="3"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="16"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -971,7 +971,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="13"/>
-      <c r="B20" s="16"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
@@ -1067,17 +1067,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
